--- a/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,384 +710,6 @@
         <v>74.59999999999999</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Black Plastic Tongs 9"</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27.94</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>19228</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tong - 6.25" (Black)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="E18" t="n">
-        <v>34.39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>26123</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sterno</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="E19" t="n">
-        <v>46.81</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>41787</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cont Anchor - 12oz (microwavable)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>97.18000000000001</v>
-      </c>
-      <c r="E20" t="n">
-        <v>194.36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>41820</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Container - Anchor (32oz)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="E21" t="n">
-        <v>102.68</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>35130</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Foil Roll - 18"</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="E22" t="n">
-        <v>26.15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>41791</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Lid Anchor - 12oz (Dome)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>107.84</v>
-      </c>
-      <c r="E23" t="n">
-        <v>215.68</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1184</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lid Anchor - 32oz (Dome) for white</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="E24" t="n">
-        <v>51.09</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>29422</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cont Salad - 32oz Sabert (Round)</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>63.89</v>
-      </c>
-      <c r="E25" t="n">
-        <v>127.78</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>41788</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Container - Anchor (16oz)</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="E26" t="n">
-        <v>90.95999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>41789</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Container - Anchor (24oz)</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="E27" t="n">
-        <v>47.76</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>22435</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Container - Deli (16oz)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="E28" t="n">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>15509</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Container - Deli (32oz)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>64.73999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>64.73999999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>22434</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Container - Deli (8oz)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="E30" t="n">
-        <v>34.29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>14909</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lid - Deli (6/32oz)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="E31" t="n">
-        <v>26.81</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>41792</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Lid Anchor - 16/24oz (Dome)</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="E32" t="n">
-        <v>40.83</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2686</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Lid Salad - 24/32oz Sabert (Round)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="E33" t="n">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Tamper Evident - 12oz Bowl (Smoothie)</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>35.62</v>
-      </c>
-      <c r="E34" t="n">
-        <v>35.62</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
